--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C2" t="n">
+        <v>305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +511,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C3" t="n">
+        <v>703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -550,10 +546,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -587,10 +581,8 @@
           <t>กรมควบคุมโรค</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -624,10 +616,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -647,6 +637,302 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc67f421-6a04-4d2e-a71d-174ba7a16b0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อกล้องโทรทัศน์วงจรปิด (CCTV) พร้อมบริการติดตั้งที่อาคารศูนย์เรียนรู้สุขภาวะ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a6f3925-f643-44ea-a79b-92ba1ae3f2e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการพัฒนาระบบสารบรรณอิเล็กทรอนิกส์แบบไร้เอกสาร (e-Office Paperless) ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c8fa5b0-f2ce-42a8-a9eb-8c3d9b669569</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการจัดหาระบบคอมพิวเตอร์เพื่อเพิ่มประสิทธิภาพระบบพิธีการศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b2af4e6-a4ee-44b7-8631-8cbb23a15e2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตู้เหล็ก MDB ขนาด 2,100 x 2,100 x 600 mm. และอื่นๆ รวม ๔๕ รายการ พร้อมติดตั้ง สำหรับงานปรับปรุงระบบหม้อแปลงไฟฟ้าและงานระบบไฟฟ้าโครงการห้องควบคุมไฟฟ้า สำนักงานชลประทานที่ ๑๕ ตำบลปากพนังฝั่งตะวันตก อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>★ (ตู้เหล็ก)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c79578e6-e9b9-4331-a83c-9a007158a3bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของกองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152080c0-8a57-4ba9-b301-257ec342ba25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์เพื่อเพิ่มประสิทธิภาพในการบริหารจัดการการทำงานของคนต่างด้าวและทดแทนเครื่องที่เสื่อมสภาพการใช้งาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ครั้งที่ ๒ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ef2d1dd-18bc-4113-aeed-d273a53d4e6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อน้ำดื่ม กลุ่มอาคารสำนักงานกลางและศูนย์แห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>★ (น้ำดื่ม)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18c5b3a9-5db7-4ecc-9043-9534b523ffbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการ รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7c4d2b9-ce6f-4ac7-8f71-3f02375abf66</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,10 +651,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C7" t="n">
+        <v>117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -688,10 +686,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C8" t="n">
+        <v>305</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -725,10 +721,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C9" t="n">
+        <v>305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -762,10 +756,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C10" t="n">
+        <v>703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -799,10 +791,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C11" t="n">
+        <v>806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -836,10 +826,8 @@
           <t>กรมการจัดหางาน</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -873,10 +861,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -910,10 +896,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -933,6 +917,228 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7c4d2b9-ce6f-4ac7-8f71-3f02375abf66</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการเช่าลิขสิทธิ์ซอฟต์แวร์ Adobe Creative Cloud For Teams ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a9a20633-733e-45b9-a64b-f30ac6c36cce</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างดำเนินโครงการห้องสมุดอาเซียน เพื่อประชาชนและเยาวชนไทย ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d060f6e3-6e29-4e24-81ed-a62434e7c617</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างซ่อมเครื่องทำน้ำเย็น ขนาดไม่น้อยกว่า 150 ตันความเย็น ยี่ห้อ Hitachi หมายเลขครุภัณฑ์ 0612-09-10-009-0001/54 จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, เครื่องทำน้ำเย็น)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f861817-5cd5-4ead-a1f7-c15761838560</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ประกอบอาคารสำนักงานสหกรณ์จังหวัดสุโขทัย และสิ่งก่อสร้างประกอบ สำนักงานสหกรณ์จังหวัดสุโขทัย ตำบลธานี อำเภอเมืองสุโขทัย จังหวัดสุโขทัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=040153d4-0892-49b6-9040-5eb5e17fa308</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทางการแพทย์ จำนวน 2 รายการ สำหรับโครงการกระบี่ Wellness City Destination ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b69edfd5-3489-46e8-bb1b-64c28104c22e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างสื่อสารเสริมสร้างความเชื่อมั่นต่อการคุ้มครองผู้บริโภคผ่านสื่อโทรทัศน์และสื่อออนไลน์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a85aac1-f0a9-4e31-bd7e-f73bb7cb0bd2</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,10 +931,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C15" t="n">
+        <v>307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -968,10 +966,8 @@
           <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+      <c r="C16" t="n">
+        <v>402</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1005,10 +1001,8 @@
           <t>กรมปศุสัตว์</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+      <c r="C17" t="n">
+        <v>706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1042,10 +1036,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C18" t="n">
+        <v>712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1079,10 +1071,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2102</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1116,10 +1106,8 @@
           <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2110</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1139,6 +1127,339 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a85aac1-f0a9-4e31-bd7e-f73bb7cb0bd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งระบบแรงดันลบภายในห้องฉุกเฉิน และภายในหอผู้ป่วย ของ โรงพยาบาลค่ายกาวิละ จังหวัดเชียงใหม่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (กาว)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f281d4-e767-4947-839b-4080c423dae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อระบบกล้องโทรทัศน์วงจรปิดและอุปกรณ์พร้อมติดตั้ง จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65229509-2960-4dd4-8de4-3dcd4ee872a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างติดตั้งกันสาดระเบียงหน้าอาคารฝึกอาชีพเย็บผ้า หลังอาคารฝึกอาชีพเย็บผ้า และหน้าอาคารโรงงานผลิตน้ำดื่ม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>★ (น้ำดื่ม)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed11f09d-fa7a-4728-8541-e70c5a9d9c39</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=324544b4-6ae6-4c3b-823e-b7f822de6576</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=98d0c097-c933-49c8-af8e-e426e478ec0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ยี่ห้อ Canon จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c347ae9-b5c0-4fee-8c1d-40b23b1fc41a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศทดแทน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60283dcc-72a9-43a6-840d-67203ba64e8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a52d7522-41b6-483f-bcfa-137168aa1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e1a2f18-fc5c-4cd4-8e93-81f0b6d37259</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,10 +1141,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C21" t="n">
+        <v>204</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1178,10 +1176,8 @@
           <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0607</t>
-        </is>
+      <c r="C22" t="n">
+        <v>607</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1215,10 +1211,8 @@
           <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0607</t>
-        </is>
+      <c r="C23" t="n">
+        <v>607</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1252,10 +1246,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C24" t="n">
+        <v>703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1289,10 +1281,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C25" t="n">
+        <v>806</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1326,10 +1316,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1363,10 +1351,8 @@
           <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1400,10 +1386,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C28" t="n">
+        <v>1706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1437,29 +1421,323 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e1a2f18-fc5c-4cd4-8e93-81f0b6d37259</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างออกแบบแนวคิดสร้างสรรค์ ประจำปี 2569 โครงการรณรงค์ส่งเสริมวิถีคนรุ่นใหม่ไร้แอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>★ (แอลกอฮอล์)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbad5b71-140e-4e92-8efe-5c3009d921b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0139</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อสิทธิโปรแกรมสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>★ (โปรแกรมสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3d75f1b-9ac3-4b49-abe4-2d9e13b1ba22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่าย (Layer 2 และ Layer 3 Switch) และอุปกรณ์บริหารจัดการเครือข่ายคอมพิวเตอร์สำหรับโครงสร้างพื้นฐานด้านเทคโนโลยีแบบบูรณาการอาคารศรีอยุธยา กระทรวงการต่างประเทศ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9be912df-6e45-4f95-8316-ff5d37f88c65</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการเพิ่มประสิทธิภาพห้องควบคุมคอมพิวเตอร์แม่ข่ายและระบบเครือข่าย (Data Center)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b362be81-5e90-4200-ada0-3eb8081b4e8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แม่ข่ายประมวลผลระบบวิเคราะห์สมดุลน้ำระดับลุ่มน้ำ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8eed8223-8105-42b4-aa75-a1d1cbd29ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ จำนวน ๑ เครื่อง สำหรับโรงพยาบาลแม่ลาน้อย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e1a2f18-fc5c-4cd4-8e93-81f0b6d37259</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed28a1f1-c625-4f1d-b470-a3549883c487</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>กรมสุขภาพจิต</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซอฟต์แวร์ปัญญาประดิษฐ์เพื่อใช้ในสำนักงาน จำนวน ๕๐ สิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2cce18b-8f7e-46d7-b433-790acd9f0277</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,10 +1456,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C30" t="n">
+        <v>117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1493,10 +1491,8 @@
           <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0139</t>
-        </is>
+      <c r="C31" t="n">
+        <v>139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1530,10 +1526,8 @@
           <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+      <c r="C32" t="n">
+        <v>402</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1567,10 +1561,8 @@
           <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0904</t>
-        </is>
+      <c r="C33" t="n">
+        <v>904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1604,10 +1596,8 @@
           <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
+      <c r="C34" t="n">
+        <v>1912</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1641,10 +1631,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C35" t="n">
+        <v>2102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1678,10 +1666,8 @@
           <t>กรมสุขภาพจิต</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
+      <c r="C36" t="n">
+        <v>2108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1715,27 +1701,321 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="n">
+        <v>2117</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างออกแบบแนวคิดสร้างสรรค์ ประจำปี 2569 โครงการรณรงค์ส่งเสริมวิถีคนรุ่นใหม่ไร้แอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★ (แอลกอฮอล์)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbad5b71-140e-4e92-8efe-5c3009d921b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0139</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อสิทธิโปรแกรมสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>★ (โปรแกรมสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3d75f1b-9ac3-4b49-abe4-2d9e13b1ba22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่าย (Layer 2 และ Layer 3 Switch) และอุปกรณ์บริหารจัดการเครือข่ายคอมพิวเตอร์สำหรับโครงสร้างพื้นฐานด้านเทคโนโลยีแบบบูรณาการอาคารศรีอยุธยา กระทรวงการต่างประเทศ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9be912df-6e45-4f95-8316-ff5d37f88c65</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการเพิ่มประสิทธิภาพห้องควบคุมคอมพิวเตอร์แม่ข่ายและระบบเครือข่าย (Data Center)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b362be81-5e90-4200-ada0-3eb8081b4e8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แม่ข่ายประมวลผลระบบวิเคราะห์สมดุลน้ำระดับลุ่มน้ำ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8eed8223-8105-42b4-aa75-a1d1cbd29ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ จำนวน ๑ เครื่อง สำหรับโรงพยาบาลแม่ลาน้อย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed28a1f1-c625-4f1d-b470-a3549883c487</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>กรมสุขภาพจิต</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซอฟต์แวร์ปัญญาประดิษฐ์เพื่อใช้ในสำนักงาน จำนวน ๕๐ สิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2cce18b-8f7e-46d7-b433-790acd9f0277</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>2117</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
         </is>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,22 +1728,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างออกแบบแนวคิดสร้างสรรค์ ประจำปี 2569 โครงการรณรงค์ส่งเสริมวิถีคนรุ่นใหม่ไร้แอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องมือช่างเกือกสัตว์ จำนวน 19 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1753,34 +1753,34 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (เครื่องมือช่าง)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbad5b71-140e-4e92-8efe-5c3009d921b7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af0e35d5-0174-47c6-9648-2fa4576aee65</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0139</t>
+          <t>0305</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อสิทธิโปรแกรมสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการเพิ่มประสิทธิภาพการบริหารงานศุลกากรด้วยระบบเทคโนโลยีสารสนเทศ สำหรับสิทธิประโยชน์ทางภาษีอากร (e-Tax Incentives) ส่วนที่ ๑ การพัฒนาระบบ e-Tax Incentive ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1790,34 +1790,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (โปรแกรมสำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3d75f1b-9ac3-4b49-abe4-2d9e13b1ba22</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66734bca-3ffe-40db-bf51-5c01e3f0c8ff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมกิจการผู้สูงอายุ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0608</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่าย (Layer 2 และ Layer 3 Switch) และอุปกรณ์บริหารจัดการเครือข่ายคอมพิวเตอร์สำหรับโครงสร้างพื้นฐานด้านเทคโนโลยีแบบบูรณาการอาคารศรีอยุธยา กระทรวงการต่างประเทศ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์เพื่อใช้ในราชการ ของกองบริหารกองทุนผู้สูงอายุ) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1827,34 +1827,34 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9be912df-6e45-4f95-8316-ff5d37f88c65</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a00dc8dc-ae3c-436b-b38a-631ffe3de342</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สำนักงานการบินพลเรือนแห่งประเทศไทย</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0904</t>
+          <t>0811</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการเพิ่มประสิทธิภาพห้องควบคุมคอมพิวเตอร์แม่ข่ายและระบบเครือข่าย (Data Center)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์เพื่อรองรับการปฏิบัติงานสำหรับผู้ตรวจสอบ เจ้าหน้าที่เทคนิค และพนักงาน กพท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1869,29 +1869,29 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b362be81-5e90-4200-ada0-3eb8081b4e8d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aa199695-df3c-4490-bd3a-a70d446c9ff8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แม่ข่ายประมวลผลระบบวิเคราะห์สมดุลน้ำระดับลุ่มน้ำ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สำหรับพัฒนาแพลตฟอร์มบริการเทคโนโลยีปัญญาประดิษฐ์ ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ ชุดเครื่องคอมพิวเตอร์แม่ข่ายบริการเทคโนโลยี AI (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1901,19 +1901,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8eed8223-8105-42b4-aa75-a1d1cbd29ba5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a13d58d7-d769-4579-9806-3341d98792b6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ จำนวน ๑ เครื่อง สำหรับโรงพยาบาลแม่ลาน้อย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1943,29 +1943,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed28a1f1-c625-4f1d-b470-a3549883c487</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7fb7620-2222-4db2-83e2-979a10858a91</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>กรมสุขภาพจิต</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซอฟต์แวร์ปัญญาประดิษฐ์เพื่อใช้ในสำนักงาน จำนวน ๕๐ สิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน (เครื่องปรับอากาศพร้อมติดตั้ง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1975,49 +1975,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2cce18b-8f7e-46d7-b433-790acd9f0277</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>สถาบันพระบรมราชชนก</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9af9775e-fced-4dd4-bf25-b61c87858913</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1736,10 +1736,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C38" t="n">
+        <v>204</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1773,10 +1771,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C39" t="n">
+        <v>305</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1810,10 +1806,8 @@
           <t>กรมกิจการผู้สูงอายุ</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0608</t>
-        </is>
+      <c r="C40" t="n">
+        <v>608</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1847,10 +1841,8 @@
           <t>สำนักงานการบินพลเรือนแห่งประเทศไทย</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0811</t>
-        </is>
+      <c r="C41" t="n">
+        <v>811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1884,10 +1876,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C42" t="n">
+        <v>1905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1921,10 +1911,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1958,29 +1946,138 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน (เครื่องปรับอากาศพร้อมติดตั้ง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9af9775e-fced-4dd4-bf25-b61c87858913</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>สำนักงานปรมาณูเพื่อสันติ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=affeda42-ba61-4c49-ba47-bcc7731bce04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน (เครื่องปรับอากาศพร้อมติดตั้ง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9af9775e-fced-4dd4-bf25-b61c87858913</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3ef64d7-d4f9-4f63-91f8-4f196a45e1a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5795aeb0-eeed-46cd-a926-ef5277f07cb2</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,10 +1981,8 @@
           <t>สำนักงานปรมาณูเพื่อสันติ</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
+      <c r="C45" t="n">
+        <v>1904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2018,10 +2016,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2102</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2055,29 +2051,212 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5795aeb0-eeed-46cd-a926-ef5277f07cb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ ศูนย์การทหารม้า จังหวัดสระบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=517561ee-194a-4867-9f4f-dc671ea07c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27384d8b-e0f6-4af6-adad-8853f2df75d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=938445f6-9f46-4178-b5b8-412e25ee4167</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ที่ได้รับการสนับสนุนจากเงินกองทุนพัฒนาไฟฟ้าในเขตพื้นที่ประกาศกองทุนพัฒนาไฟฟ้าพลังความร้อนร่วม พระนครเหนือ ศูนย์ส่งเสริมการเรียนรู้ระดับเขตพระนคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ed4eb22-8577-45fc-abe5-0b8918af278b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อประกวดราคาครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ รายการรถตู้ (ดีเซล) ไม่เกิน 12 ที่นั่ง ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี จำนวน 1 คัน วงเงิน 2,000,000.-บาท โดยวิธีอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5795aeb0-eeed-46cd-a926-ef5277f07cb2</t>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b102bff-0020-4f91-acda-561dd332a1fb</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>806</v>
+        <v>1503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ยี่ห้อ Canon จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=98d0c097-c933-49c8-af8e-e426e478ec0b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c347ae9-b5c0-4fee-8c1d-40b23b1fc41a</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1503</v>
+        <v>1705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ยี่ห้อ Canon จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศทดแทน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c347ae9-b5c0-4fee-8c1d-40b23b1fc41a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60283dcc-72a9-43a6-840d-67203ba64e8b</t>
         </is>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศทดแทน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60283dcc-72a9-43a6-840d-67203ba64e8b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a52d7522-41b6-483f-bcfa-137168aa1332</t>
         </is>
       </c>
     </row>
@@ -1383,15 +1383,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1706</v>
+        <v>2102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1406,27 +1406,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a52d7522-41b6-483f-bcfa-137168aa1332</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e1a2f18-fc5c-4cd4-8e93-81f0b6d37259</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2102</v>
+        <v>117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างออกแบบแนวคิดสร้างสรรค์ ประจำปี 2569 โครงการรณรงค์ส่งเสริมวิถีคนรุ่นใหม่ไร้แอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e1a2f18-fc5c-4cd4-8e93-81f0b6d37259</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbad5b71-140e-4e92-8efe-5c3009d921b7</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+          <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างออกแบบแนวคิดสร้างสรรค์ ประจำปี 2569 โครงการรณรงค์ส่งเสริมวิถีคนรุ่นใหม่ไร้แอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อสิทธิโปรแกรมสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (โปรแกรมสำนักงาน)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbad5b71-140e-4e92-8efe-5c3009d921b7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3d75f1b-9ac3-4b49-abe4-2d9e13b1ba22</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการการรักษาความมั่นคงปลอดภัยไซเบอร์แห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อสิทธิโปรแกรมสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่าย (Layer 2 และ Layer 3 Switch) และอุปกรณ์บริหารจัดการเครือข่ายคอมพิวเตอร์สำหรับโครงสร้างพื้นฐานด้านเทคโนโลยีแบบบูรณาการอาคารศรีอยุธยา กระทรวงการต่างประเทศ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (โปรแกรมสำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3d75f1b-9ac3-4b49-abe4-2d9e13b1ba22</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9be912df-6e45-4f95-8316-ff5d37f88c65</t>
         </is>
       </c>
     </row>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>402</v>
+        <v>904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่าย (Layer 2 และ Layer 3 Switch) และอุปกรณ์บริหารจัดการเครือข่ายคอมพิวเตอร์สำหรับโครงสร้างพื้นฐานด้านเทคโนโลยีแบบบูรณาการอาคารศรีอยุธยา กระทรวงการต่างประเทศ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการเพิ่มประสิทธิภาพห้องควบคุมคอมพิวเตอร์แม่ข่ายและระบบเครือข่าย (Data Center)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9be912df-6e45-4f95-8316-ff5d37f88c65</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b362be81-5e90-4200-ada0-3eb8081b4e8d</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>904</v>
+        <v>1912</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการเพิ่มประสิทธิภาพห้องควบคุมคอมพิวเตอร์แม่ข่ายและระบบเครือข่าย (Data Center)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แม่ข่ายประมวลผลระบบวิเคราะห์สมดุลน้ำระดับลุ่มน้ำ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b362be81-5e90-4200-ada0-3eb8081b4e8d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8eed8223-8105-42b4-aa75-a1d1cbd29ba5</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>สถาบันสารสนเทศทรัพยากรน้ำ (องค์การมหาชน)</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1912</v>
+        <v>2102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แม่ข่ายประมวลผลระบบวิเคราะห์สมดุลน้ำระดับลุ่มน้ำ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ จำนวน ๑ เครื่อง สำหรับโรงพยาบาลแม่ลาน้อย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8eed8223-8105-42b4-aa75-a1d1cbd29ba5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed28a1f1-c625-4f1d-b470-a3549883c487</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสุขภาพจิต</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ จำนวน ๑ เครื่อง สำหรับโรงพยาบาลแม่ลาน้อย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซอฟต์แวร์ปัญญาประดิษฐ์เพื่อใช้ในสำนักงาน จำนวน ๕๐ สิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed28a1f1-c625-4f1d-b470-a3549883c487</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2cce18b-8f7e-46d7-b433-790acd9f0277</t>
         </is>
       </c>
     </row>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>กรมสุขภาพจิต</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2108</v>
+        <v>2117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซอฟต์แวร์ปัญญาประดิษฐ์เพื่อใช้ในสำนักงาน จำนวน ๕๐ สิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1681,32 +1681,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2cce18b-8f7e-46d7-b433-790acd9f0277</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2117</v>
+        <v>204</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องมือช่างเกือกสัตว์ จำนวน 19 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องมือช่าง)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d176a015-e0ff-4eb1-bc89-f91ee05f5f7b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af0e35d5-0174-47c6-9648-2fa4576aee65</t>
         </is>
       </c>
     </row>
@@ -1733,15 +1733,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องมือช่างเกือกสัตว์ จำนวน 19 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการเพิ่มประสิทธิภาพการบริหารงานศุลกากรด้วยระบบเทคโนโลยีสารสนเทศ สำหรับสิทธิประโยชน์ทางภาษีอากร (e-Tax Incentives) ส่วนที่ ๑ การพัฒนาระบบ e-Tax Incentive ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (เครื่องมือช่าง)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af0e35d5-0174-47c6-9648-2fa4576aee65</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66734bca-3ffe-40db-bf51-5c01e3f0c8ff</t>
         </is>
       </c>
     </row>
@@ -1768,15 +1768,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมกิจการผู้สูงอายุ</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>305</v>
+        <v>608</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการเพิ่มประสิทธิภาพการบริหารงานศุลกากรด้วยระบบเทคโนโลยีสารสนเทศ สำหรับสิทธิประโยชน์ทางภาษีอากร (e-Tax Incentives) ส่วนที่ ๑ การพัฒนาระบบ e-Tax Incentive ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์เพื่อใช้ในราชการ ของกองบริหารกองทุนผู้สูงอายุ) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66734bca-3ffe-40db-bf51-5c01e3f0c8ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a00dc8dc-ae3c-436b-b38a-631ffe3de342</t>
         </is>
       </c>
     </row>
@@ -1803,15 +1803,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>กรมกิจการผู้สูงอายุ</t>
+          <t>สำนักงานการบินพลเรือนแห่งประเทศไทย</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>608</v>
+        <v>811</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์เพื่อใช้ในราชการ ของกองบริหารกองทุนผู้สูงอายุ) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์เพื่อรองรับการปฏิบัติงานสำหรับผู้ตรวจสอบ เจ้าหน้าที่เทคนิค และพนักงาน กพท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a00dc8dc-ae3c-436b-b38a-631ffe3de342</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aa199695-df3c-4490-bd3a-a70d446c9ff8</t>
         </is>
       </c>
     </row>
@@ -1838,15 +1838,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>สำนักงานการบินพลเรือนแห่งประเทศไทย</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>811</v>
+        <v>1905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าคอมพิวเตอร์เพื่อรองรับการปฏิบัติงานสำหรับผู้ตรวจสอบ เจ้าหน้าที่เทคนิค และพนักงาน กพท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สำหรับพัฒนาแพลตฟอร์มบริการเทคโนโลยีปัญญาประดิษฐ์ ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ ชุดเครื่องคอมพิวเตอร์แม่ข่ายบริการเทคโนโลยี AI (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aa199695-df3c-4490-bd3a-a70d446c9ff8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a13d58d7-d769-4579-9806-3341d98792b6</t>
         </is>
       </c>
     </row>
@@ -1873,15 +1873,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1905</v>
+        <v>2102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบครุภัณฑ์สำหรับพัฒนาแพลตฟอร์มบริการเทคโนโลยีปัญญาประดิษฐ์ ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ ชุดเครื่องคอมพิวเตอร์แม่ข่ายบริการเทคโนโลยี AI (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a13d58d7-d769-4579-9806-3341d98792b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7fb7620-2222-4db2-83e2-979a10858a91</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน (เครื่องปรับอากาศพร้อมติดตั้ง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,32 +1926,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7fb7620-2222-4db2-83e2-979a10858a91</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9af9775e-fced-4dd4-bf25-b61c87858913</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานปรมาณูเพื่อสันติ</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2102</v>
+        <v>1904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน (เครื่องปรับอากาศพร้อมติดตั้ง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9af9775e-fced-4dd4-bf25-b61c87858913</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=affeda42-ba61-4c49-ba47-bcc7731bce04</t>
         </is>
       </c>
     </row>
@@ -1978,15 +1978,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>สำนักงานปรมาณูเพื่อสันติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1904</v>
+        <v>2102</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=affeda42-ba61-4c49-ba47-bcc7731bce04</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3ef64d7-d4f9-4f63-91f8-4f196a45e1a6</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2036,27 +2036,27 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3ef64d7-d4f9-4f63-91f8-4f196a45e1a6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5795aeb0-eeed-46cd-a926-ef5277f07cb2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2102</v>
+        <v>204</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ ศูนย์การทหารม้า จังหวัดสระบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5795aeb0-eeed-46cd-a926-ef5277f07cb2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=517561ee-194a-4867-9f4f-dc671ea07c90</t>
         </is>
       </c>
     </row>
@@ -2083,17 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>703</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ ศูนย์การทหารม้า จังหวัดสระบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2103,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=517561ee-194a-4867-9f4f-dc671ea07c90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27384d8b-e0f6-4af6-adad-8853f2df75d2</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2118,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>806</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2140,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27384d8b-e0f6-4af6-adad-8853f2df75d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=938445f6-9f46-4178-b5b8-412e25ee4167</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2153,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2033</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ที่ได้รับการสนับสนุนจากเงินกองทุนพัฒนาไฟฟ้าในเขตพื้นที่ประกาศกองทุนพัฒนาไฟฟ้าพลังความร้อนร่วม พระนครเหนือ ศูนย์ส่งเสริมการเรียนรู้ระดับเขตพระนคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2182,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=938445f6-9f46-4178-b5b8-412e25ee4167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ed4eb22-8577-45fc-abe5-0b8918af278b</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2188,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2102</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ที่ได้รับการสนับสนุนจากเงินกองทุนพัฒนาไฟฟ้าในเขตพื้นที่ประกาศกองทุนพัฒนาไฟฟ้าพลังความร้อนร่วม พระนครเหนือ ศูนย์ส่งเสริมการเรียนรู้ระดับเขตพระนคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ รายการรถตู้ (ดีเซล) ไม่เกิน 12 ที่นั่ง ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี จำนวน 1 คัน วงเงิน 2,000,000.-บาท โดยวิธีอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2219,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ed4eb22-8577-45fc-abe5-0b8918af278b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b102bff-0020-4f91-acda-561dd332a1fb</t>
         </is>
       </c>
     </row>
@@ -2231,30 +2223,178 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ ศูนย์การทหารม้า จังหวัดสระบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=517561ee-194a-4867-9f4f-dc671ea07c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27384d8b-e0f6-4af6-adad-8853f2df75d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=938445f6-9f46-4178-b5b8-412e25ee4167</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ที่ได้รับการสนับสนุนจากเงินกองทุนพัฒนาไฟฟ้าในเขตพื้นที่ประกาศกองทุนพัฒนาไฟฟ้าพลังความร้อนร่วม พระนครเหนือ ศูนย์ส่งเสริมการเรียนรู้ระดับเขตพระนคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ed4eb22-8577-45fc-abe5-0b8918af278b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ รายการรถตู้ (ดีเซล) ไม่เกิน 12 ที่นั่ง ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี จำนวน 1 คัน วงเงิน 2,000,000.-บาท โดยวิธีอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b102bff-0020-4f91-acda-561dd332a1fb</t>
         </is>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -2218,22 +2218,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0204</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ ศูนย์การทหารม้า จังหวัดสระบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องแม่ข่ายและบริการศูนย์สำรองกู้คืนระบบ (DR Site) ประจำปี 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2243,34 +2243,34 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=517561ee-194a-4867-9f4f-dc671ea07c90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ebb95475-e1af-43fe-b30d-af8345d91e2d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0703</t>
+          <t>0305</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานปรับปรุงห้องฝึกอบรมคอมพิวเตอร์ 405 ศูนย์เทคโนโลยีสารสนเทศและการสื่อสาร กรมชลประทาน สามเสน ตามโครงการเพิ่มประสิทธิภาพการบริหารจัดการระบบเทคโนโลยีสารสนเทศและการสื่อสารสำหรับงานชลประทาน ระยะที่ 9 กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการปรับปรุงประสิทธิภาพระบบเครือข่ายหลักสำหรับศูนย์คอมพิวเตอร์กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2285,29 +2285,29 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27384d8b-e0f6-4af6-adad-8853f2df75d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7d726aa-e13e-449c-b574-ef396b19e56c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0806</t>
+          <t>0804</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 20 รายการ เพื่อใช้ในงานปรับปรุงอาคารที่ทำการ สำนักบริหารบำรุงทาง กรมทางหลวง พญาไท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างออกแบบผลิตและเผยแพร่การประชาสัมพันธ์พันธกิจของกองทุนเพื่อความปลอดภัยในการใช้รถใช้ถนน ด้านการมอบอุปกรณ์สำหรับผู้พิการผ่านรายการโทรทัศน์ในรูปแบบสกู๊ป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2317,34 +2317,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=938445f6-9f46-4178-b5b8-412e25ee4167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c7cc953c-6576-455d-af23-04b7f2c7858f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ที่ได้รับการสนับสนุนจากเงินกองทุนพัฒนาไฟฟ้าในเขตพื้นที่ประกาศกองทุนพัฒนาไฟฟ้าพลังความร้อนร่วม พระนครเหนือ ศูนย์ส่งเสริมการเรียนรู้ระดับเขตพระนคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน สำนักงานประกันสังคมจังหวัดเชียงใหม่ และสาขาฝาง ประจำปี 2569 (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2354,34 +2354,34 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ed4eb22-8577-45fc-abe5-0b8918af278b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5efea1dc-d0f3-47e8-ad2c-8a3aee6f0fa5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ รายการรถตู้ (ดีเซล) ไม่เกิน 12 ที่นั่ง ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี จำนวน 1 คัน วงเงิน 2,000,000.-บาท โดยวิธีอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 19 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b102bff-0020-4f91-acda-561dd332a1fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=20e03fbf-7703-4bb3-b17b-72104de598f7</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2226,10 +2226,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C52" t="n">
+        <v>117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2263,10 +2261,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C53" t="n">
+        <v>305</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2300,10 +2296,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C54" t="n">
+        <v>804</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2337,10 +2331,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C55" t="n">
+        <v>1706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2374,10 +2366,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2397,6 +2387,302 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=20e03fbf-7703-4bb3-b17b-72104de598f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตภาพยนตร์โฆษณาสื่อโทรทัศน์และสื่อดิจิทัล ประจำปี 2569 โครงการรณรงค์สร้างความเข้าใจเกี่ยวกับนโยบายควบคุมเครื่องดื่มแอลกอฮอล์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์, แอลกอฮอล์)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5877fc43-c57a-4b6d-baa6-4168df645d7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตภาพยนตร์โฆษณาสื่อโทรทัศน์และสื่อดิจิทัล ประจำปี 2569 โครงการรณรงค์สร้างความเข้าใจภายในครอบครัวลดปัญหาสุขภาพจิต ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=67c84830-a057-4ed0-a5d4-f635b7e04637</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตภาพยนตร์โฆษณาสื่อโทรทัศน์และสื่อดิจิทัล ประจำปี 2569 โครงการรณรงค์ปรับพฤติกรรมลดเสี่ยง NCDs ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6116693d-5e08-4c7f-8985-39287f6f15de</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตภาพยนตร์โฆษณาสื่อโทรทัศน์และสื่อดิจิทัล ประจำปี 2569 โครงการรณรงค์ส่งเสริมกิจกรรมทางกายร่วมกับงาน THAI HEALTH DAY RUN ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03640b54-c71d-4938-bc7b-fcca7bb4604e</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0137</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์ครุภัณฑ์คอมพิวเตอร์สำหรับให้บริการและสนับสนุนการทำงานของเจ้าหน้าที่ สำหรับศูนย์สร้างสรรค์งานออกแบบ (TCDC) แห่งใหม่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97cc8441-ca1a-4662-be60-043e0b42162d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อคอมพิวเตอร์แท็บเล็ต จำนวน ๘๗ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, แท็บเล็ต)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b3d04f8-2874-4dbc-93b5-65bdf5d60a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถยนต์ไฟฟ้า ประเภทปลั๊กอินไฮบริด (PHEV) สำนักงานสาธารณสุขจังหวัดนครปฐม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=76326e0f-b85f-43df-8ffe-d293e350e6ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad38f2bb-e372-42da-b5ad-b6d015f05a6b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2401,10 +2401,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C57" t="n">
+        <v>117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2438,10 +2436,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C58" t="n">
+        <v>117</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2475,10 +2471,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C59" t="n">
+        <v>117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2512,10 +2506,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C60" t="n">
+        <v>117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2549,10 +2541,8 @@
           <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0137</t>
-        </is>
+      <c r="C61" t="n">
+        <v>137</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2586,10 +2576,8 @@
           <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="C62" t="n">
+        <v>1202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2623,10 +2611,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C63" t="n">
+        <v>2102</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2660,29 +2646,175 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad38f2bb-e372-42da-b5ad-b6d015f05a6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์ยานพาหนะรถโดยสารขนาด 12 ที่นั่ง (เครื่องยนต์ดีเซล) ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 90 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffd1b419-188f-417e-9bf4-04a1656e9c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084ee673-5142-4495-8231-3b4d80021e2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad38f2bb-e372-42da-b5ad-b6d015f05a6b</t>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e140fe58-cc5d-4b75-b46c-7cffa5df7138</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2681,10 +2681,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C65" t="n">
+        <v>806</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2718,10 +2716,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2755,10 +2751,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C67" t="n">
+        <v>2102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2792,27 +2786,247 @@
           <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" t="n">
+        <v>2113</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงห้องประชุม 3, 4 (ห้องปฏิบัติการคอมพิวเตอร์) และบริเวณห้องโถง อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89fb1dce-52ab-4e8c-b345-4ca292d218c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า พร้อมอุปกรณ์ประกอบ จำนวน 4 รายการ สำหรับสถานีสูบน้ำด้วยไฟฟ้าพนังกั้นน้ำ Dike-11 บ้านห้วย ตำบลบัวหุ่ง อำเภอราษีไศล จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=835fb573-89bf-4db3-ad34-aef9ca9d9431</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์ยานพาหนะรถโดยสารขนาด 12 ที่นั่ง (เครื่องยนต์ดีเซล) ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 90 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffd1b419-188f-417e-9bf4-04a1656e9c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084ee673-5142-4495-8231-3b4d80021e2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e140fe58-cc5d-4b75-b46c-7cffa5df7138</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
         </is>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2678,15 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>806</v>
+        <v>304</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์ยานพาหนะรถโดยสารขนาด 12 ที่นั่ง (เครื่องยนต์ดีเซล) ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 90 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงห้องประชุม 3, 4 (ห้องปฏิบัติการคอมพิวเตอร์) และบริเวณห้องโถง อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffd1b419-188f-417e-9bf4-04a1656e9c12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89fb1dce-52ab-4e8c-b345-4ca292d218c1</t>
         </is>
       </c>
     </row>
@@ -2713,15 +2713,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1706</v>
+        <v>703</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า พร้อมอุปกรณ์ประกอบ จำนวน 4 รายการ สำหรับสถานีสูบน้ำด้วยไฟฟ้าพนังกั้นน้ำ Dike-11 บ้านห้วย ตำบลบัวหุ่ง อำเภอราษีไศล จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084ee673-5142-4495-8231-3b4d80021e2b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=835fb573-89bf-4db3-ad34-aef9ca9d9431</t>
         </is>
       </c>
     </row>
@@ -2748,15 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2102</v>
+        <v>806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์ยานพาหนะรถโดยสารขนาด 12 ที่นั่ง (เครื่องยนต์ดีเซล) ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 90 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e140fe58-cc5d-4b75-b46c-7cffa5df7138</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffd1b419-188f-417e-9bf4-04a1656e9c12</t>
         </is>
       </c>
     </row>
@@ -2783,15 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2113</v>
+        <v>1706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084ee673-5142-4495-8231-3b4d80021e2b</t>
         </is>
       </c>
     </row>
@@ -2818,17 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2102</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการปรับปรุงห้องประชุม 3, 4 (ห้องปฏิบัติการคอมพิวเตอร์) และบริเวณห้องโถง อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2838,12 +2836,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89fb1dce-52ab-4e8c-b345-4ca292d218c1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e140fe58-cc5d-4b75-b46c-7cffa5df7138</t>
         </is>
       </c>
     </row>
@@ -2855,17 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2113</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า พร้อมอุปกรณ์ประกอบ จำนวน 4 รายการ สำหรับสถานีสูบน้ำด้วยไฟฟ้าพนังกั้นน้ำ Dike-11 บ้านห้วย ตำบลบัวหุ่ง อำเภอราษีไศล จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2875,34 +2871,34 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=835fb573-89bf-4db3-ad34-aef9ca9d9431</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0806</t>
+          <t>0137</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์ยานพาหนะรถโดยสารขนาด 12 ที่นั่ง (เครื่องยนต์ดีเซล) ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 90 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์ระบบเครือข่ายคอมพิวเตอร์ สำหรับศูนย์สร้างสรรค์งานออกแบบ (TCDC) แห่งใหม่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2912,34 +2908,34 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffd1b419-188f-417e-9bf4-04a1656e9c12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d890e70-862a-4b04-a120-644d2228e620</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานคณะกรรมการกำกับและส่งเสริมการประกอบธุรกิจประกันภัย</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>0313</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาระบบคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ระยะเวลา 365 วัน (ปี 2569 - 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2949,34 +2945,34 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084ee673-5142-4495-8231-3b4d80021e2b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bab9e56c-af3b-49ec-a65c-f9b5b3dca743</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊กสำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย จำนวน ๓๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2986,34 +2982,34 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e140fe58-cc5d-4b75-b46c-7cffa5df7138</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=76d871ac-adc3-47f0-b2ef-11bda4d8fce2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>สำนักงานเทคโนโลยีและนวัตกรรมด้านชีววิทยาศาสตร์ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบประชุมทางไกลออนไลน์ สำหรับห้องประชุม ชั้น 4 สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าครุภัณฑ์คอมพิวเตอร์สำหรับเจ้าหน้าที่และผู้บริหาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3023,12 +3019,49 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b9cc72c-6a1b-423f-a09c-83df500122c1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=762e8c3f-a4b0-4306-b3c2-c277e146d7fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า ๒๐ คิว จำนวน ๕ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>★ (ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f05bc9a7-d637-4c69-b5d6-1ba3560140db</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2891,10 +2891,8 @@
           <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>0137</t>
-        </is>
+      <c r="C71" t="n">
+        <v>137</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2928,10 +2926,8 @@
           <t>สำนักงานคณะกรรมการกำกับและส่งเสริมการประกอบธุรกิจประกันภัย</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>0313</t>
-        </is>
+      <c r="C72" t="n">
+        <v>313</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2965,10 +2961,8 @@
           <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
+      <c r="C73" t="n">
+        <v>1308</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3002,10 +2996,8 @@
           <t>สำนักงานเทคโนโลยีและนวัตกรรมด้านชีววิทยาศาสตร์ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
+      <c r="C74" t="n">
+        <v>1914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3039,29 +3031,397 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า ๒๐ คิว จำนวน ๕ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>★ (ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f05bc9a7-d637-4c69-b5d6-1ba3560140db</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อการจัดซื้อลิขสิทธิ์ซอฟต์แวร์ระบบสำรองข้อมูลของโครงการ Private Cloud จำนวน 100 ลิขสิทธิ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dbc26480-6092-4cee-87bf-c136dde271e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการประชาสัมพันธ์ภาพลักษณ์สินค้าและบริการไทยผ่านสื่อโทรทัศน์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e9f3305-6828-4b53-9865-9b877e59bd5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงยุติธรรม</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์แบบพกพาประสิทธิภาพสูงพร้อมซอฟต์แวร์และอุปกรณ์สำรวจพื้นที่แบบพกพาเพื่องานออกแบบก่อสร้างและประมาณราคา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3503a26-1e7d-4b4a-8f21-fb8d8dc8e917</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงานของสำนักงานประกันสังคมจังหวัดสมุทรปราการ และสำนักงานประกันสังคมจังหวัดสมุทรปราการ สาขาพระประแดง ประจำปี ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dc26bc4-0825-4b33-9426-0406f2664f73</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาเทคโนโลยีอวกาศและภูมิสารสนเทศ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์รักษาความปลอดภัยระบบเครือข่ายและซอฟต์แวร์สำหรับบริหารจัดการระบบเครือข่าย (R2026-000174) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=13075321-3a41-45d0-a107-2736c15ae00d</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า ๒๐ คิว จำนวน ๕ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>★ (ตู้เย็น)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f05bc9a7-d637-4c69-b5d6-1ba3560140db</t>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ตู้เย็นเก็บศพ 2 ศพ  (จำนวน 1 เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6755995d-6450-4064-be40-836e650d41e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์ ยูนิตทำฟัน ค่าบริการทางการแพทย์ที่เบิกจ่ายในลักษณะงบลงทุน ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd4327dc-c0de-4d40-bc14-726f2008841d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ที่มีขนาดความจุของแบตเตอรี่มากกว่า 50 - 60 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 180 กิโลวัตต์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9c0fc744-9265-44ab-ae11-dff008a30300</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=277b0c12-84c3-4b20-944f-57d35f44fa67</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ระบบเครือข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4476457f-fdef-4c0a-a068-9c94b5ea747c</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3066,10 +3066,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C76" t="n">
+        <v>705</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3103,10 +3101,8 @@
           <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
+      <c r="C77" t="n">
+        <v>1309</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3140,10 +3136,8 @@
           <t>สำนักงานปลัดกระทรวงยุติธรรม</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
+      <c r="C78" t="n">
+        <v>1602</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3177,10 +3171,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C79" t="n">
+        <v>1706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3214,10 +3206,8 @@
           <t>สำนักงานพัฒนาเทคโนโลยีอวกาศและภูมิสารสนเทศ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
+      <c r="C80" t="n">
+        <v>1906</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3251,10 +3241,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C81" t="n">
+        <v>2102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3288,10 +3276,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C82" t="n">
+        <v>2102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3325,10 +3311,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C83" t="n">
+        <v>2102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3362,10 +3346,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3399,29 +3381,249 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" t="n">
+        <v>2117</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ระบบเครือข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4476457f-fdef-4c0a-a068-9c94b5ea747c</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อจอภาพอัจฉริยะสำหรับห้องประชุมขนาดเล็ก 7 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>★ (จอภาพ)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=762adc4b-071c-4ae6-b9f6-6ec349ca562d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาเครื่องคอมพิวเตอร์และอุปกรณ์เพื่อการบริหารจัดการแผ่นป้ายทะเบียนรถของเงินทุนหมุนเวียนเพื่อจัดทำแผ่นป้ายทะเบียนรถ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc1de286-0255-499d-97bf-246e93110076</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การแพทย์-เครื่องเอกซเรย์ฟันทั้งปาก พร้อมกะโหลกศีรษะแบบ 3 มิติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1e1b3c14-cfd2-4b2f-9ea2-27a4cb1573a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>2117</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ระบบเครือข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4476457f-fdef-4c0a-a068-9c94b5ea747c</t>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การศึกษา จำนวน 3 รายการ ของคณะแพทยศาสตร์ สถาบันพระบรมราชชนก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7386d866-a0a7-4a90-b5b5-3f40d608e3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bbd86288-f6e3-4bc9-b989-d0a9188a41b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=058752a8-7491-4f67-ab49-0ee761f15295</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3416,10 +3416,8 @@
           <t>กรมบัญชีกลาง</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+      <c r="C86" t="n">
+        <v>304</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3453,10 +3451,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C87" t="n">
+        <v>804</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3490,10 +3486,8 @@
           <t>กรมอนามัย</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
+      <c r="C88" t="n">
+        <v>2109</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3527,10 +3521,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C89" t="n">
+        <v>2117</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3564,10 +3556,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C90" t="n">
+        <v>2117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3601,10 +3591,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C91" t="n">
+        <v>2117</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3624,6 +3612,117 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=058752a8-7491-4f67-ab49-0ee761f15295</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=456feb17-ac87-4165-8d7d-07ee6dc8d841</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า ๓๐๐ mA ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d211f496-cf05-45e0-9645-bae80288f0ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ ตู้แช่แข็งแบบพิเศษ DEEP FREEZER  (-80 องศาเซลเซียส) จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3f1a582-cd39-4d49-b077-7d5a30cfcdd6</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202607.xlsx
+++ b/Backup/eGP_Monthly_Main_202607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3626,10 +3626,8 @@
           <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+      <c r="C92" t="n">
+        <v>909</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3663,10 +3661,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C93" t="n">
+        <v>2102</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3700,27 +3696,173 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" t="n">
+        <v>2106</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ ตู้แช่แข็งแบบพิเศษ DEEP FREEZER  (-80 องศาเซลเซียส) จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3f1a582-cd39-4d49-b077-7d5a30cfcdd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=456feb17-ac87-4165-8d7d-07ee6dc8d841</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ พร้อมติดตั้ง จำนวน ๑๔ เครื่อง สำหรับใช้ในราชการหน่วยงานต่างๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c260f7e3-a3cd-427e-9cd8-1f5afde05013</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า ๓๐๐ mA ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d211f496-cf05-45e0-9645-bae80288f0ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>2106</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ ตู้แช่แข็งแบบพิเศษ DEEP FREEZER  (-80 องศาเซลเซียส) จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3f1a582-cd39-4d49-b077-7d5a30cfcdd6</t>
         </is>
